--- a/data/trans_camb/IP16A04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 1,3</t>
+          <t>-16,13; 1,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 11,08</t>
+          <t>-8,41; 10,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,0; 10,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 1,66</t>
+          <t>-6,84; 1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 7,02</t>
+          <t>-3,62; 7,6</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 6,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
     </row>
@@ -948,27 +948,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 3,88</t>
+          <t>-13,62; 3,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 0,0</t>
+          <t>-16,96; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 1,77</t>
+          <t>-7,01; 1,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,42</t>
+          <t>-7,14; 1,42</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,77</t>
+          <t>0,0; 10,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 3,81</t>
+          <t>-7,1; 3,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 8,12</t>
+          <t>-6,99; 6,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 1,71</t>
+          <t>-5,02; 1,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,93</t>
+          <t>-2,95; 5,9</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,34</t>
+          <t>-3,53; 0,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,95</t>
+          <t>-1,14; 3,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,01</t>
+          <t>-3,05; 1,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,39</t>
+          <t>-3,08; 1,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,45</t>
+          <t>-2,26; 0,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,98</t>
+          <t>-1,26; 1,98</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,66; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-91,97; 170,12</t>
+          <t>-92,22; 206,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 438,74</t>
+          <t>-66,48; 384,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 1,28</t>
+          <t>-13,98; 1,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 10,78</t>
+          <t>-8,25; 10,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,26</t>
+          <t>0,0; 12,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,85</t>
+          <t>-6,43; 1,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 7,6</t>
+          <t>-3,45; 7,72</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,07</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
     </row>
@@ -948,27 +948,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 3,86</t>
+          <t>-13,42; 3,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 0,0</t>
+          <t>-17,58; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 1,79</t>
+          <t>-7,03; 1,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,42</t>
+          <t>-6,96; 1,42</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,87</t>
+          <t>0,0; 10,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 3,93</t>
+          <t>-6,98; 3,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 6,99</t>
+          <t>-7,0; 7,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 1,66</t>
+          <t>-5,04; 1,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,9</t>
+          <t>-3,54; 5,05</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,34</t>
+          <t>-3,26; 0,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,85</t>
+          <t>-1,16; 4,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,15</t>
+          <t>-2,95; 1,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,34</t>
+          <t>-3,08; 1,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,41</t>
+          <t>-2,25; 0,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,98</t>
+          <t>-1,36; 2,12</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-73,66; —</t>
+          <t>-72,99; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-92,22; 206,83</t>
+          <t>-91,48; 139,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 384,29</t>
+          <t>-66,56; 419,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Edad-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumieron medicamentos laxantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-3,66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1,55</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 1,29</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 10,94</t>
+          <t>0,0; 10,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>-14,44; 1,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,37</t>
+          <t>-8,34; 11,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 1,4</t>
+          <t>-5,88; 1,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 7,72</t>
+          <t>-3,51; 7,02</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-74,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>31,41%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,18</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,41</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1,41</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,41</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,36; 3,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>-14,51; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 3,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 0,0</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 1,79</t>
+          <t>-8,02; 1,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,42</t>
+          <t>-8,18; 1,42</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-43,55%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-43,55%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,82</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2,13</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,62; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,47</t>
+          <t>-6,97; 8,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 7,03</t>
+          <t>0,0; 10,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,72</t>
+          <t>-5,3; 1,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 5,05</t>
+          <t>-2,89; 4,93</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-46,38%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-23,7%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-46,38%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-23,7%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,81</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,33</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,34</t>
+          <t>-3,29; 1,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,04</t>
+          <t>-3,08; 1,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,17</t>
+          <t>-3,47; 0,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,32</t>
+          <t>-1,12; 3,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,41</t>
+          <t>-2,36; 0,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,12</t>
+          <t>-1,29; 1,98</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-35,54%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-39,07%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-70,73%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>116,23%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-35,54%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-39,07%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,99; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-91,48; 139,35</t>
+          <t>-91,97; 170,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,56; 419,99</t>
+          <t>-66,95; 438,74</t>
         </is>
       </c>
     </row>
